--- a/public/assets/template/employee_template.xlsx
+++ b/public/assets/template/employee_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\hris_app_shield\public\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EC3587-B5B2-428D-8888-BFB3AB191079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470B8024-CD52-40C6-B46E-497D9D424A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Name</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>HR Partner</t>
-  </si>
-  <si>
-    <t>Emp ID</t>
   </si>
   <si>
     <t>Type</t>
@@ -152,10 +149,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FBF119AE-B9BA-45FA-B558-F911B8936FB3}" name="Table1" displayName="Table1" ref="A1:P8" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:P8" xr:uid="{FBF119AE-B9BA-45FA-B558-F911B8936FB3}"/>
-  <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{B8B20153-927E-4880-8B99-3A007791DC0B}" name="Emp ID"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FBF119AE-B9BA-45FA-B558-F911B8936FB3}" name="Table1" displayName="Table1" ref="A1:O2" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:O2" xr:uid="{FBF119AE-B9BA-45FA-B558-F911B8936FB3}"/>
+  <tableColumns count="15">
     <tableColumn id="2" xr3:uid="{6A8A6372-EBCE-47F0-8929-2F8E738F0084}" name="Name"/>
     <tableColumn id="3" xr3:uid="{38E549E1-5A31-4803-9A64-834CDFC48373}" name="Gender"/>
     <tableColumn id="18" xr3:uid="{BFCAA876-5E58-45AF-8124-5F439EAF8377}" name="Email"/>
@@ -473,59 +469,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" customWidth="1"/>
-    <col min="9" max="9" width="27" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" style="2"/>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="27" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>10</v>
@@ -533,54 +528,15 @@
       <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:16">
-      <c r="D2"/>
-      <c r="F2" s="2"/>
-      <c r="N2"/>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="D3"/>
-      <c r="F3" s="2"/>
-      <c r="N3"/>
-      <c r="P3" s="2"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="D4"/>
-      <c r="F4" s="2"/>
-      <c r="N4"/>
-      <c r="P4" s="2"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="D5"/>
-      <c r="F5" s="2"/>
-      <c r="N5"/>
-      <c r="P5" s="2"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="D6"/>
-      <c r="F6" s="2"/>
-      <c r="N6"/>
-      <c r="P6" s="2"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="D7"/>
-      <c r="F7" s="2"/>
-      <c r="N7"/>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="D8"/>
-      <c r="F8" s="2"/>
-      <c r="N8"/>
-      <c r="P8" s="2"/>
+    <row r="2" spans="1:15">
+      <c r="C2"/>
+      <c r="E2" s="2"/>
+      <c r="M2"/>
+      <c r="O2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
